--- a/iShares/IWVL/IWVL-Regressie-Developed_5_Factors.xlsx
+++ b/iShares/IWVL/IWVL-Regressie-Developed_5_Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\iShares\IWVL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9774DE5-0D36-46D3-9448-025D830C5CDD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABFDBFA-ACB4-4D54-B074-FC65B2546BC8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="0" windowWidth="38535" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="0" windowWidth="38535" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="3" r:id="rId1"/>
@@ -638,7 +638,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -653,6 +653,8 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1179,28 +1181,28 @@
       <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="8">
         <v>-0.1465964711981482</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="8">
         <v>0.13234767441321174</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="8">
         <v>-1.1076618599315113</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="8">
         <v>0.27215349114805787</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="8">
         <v>-0.41099134505340462</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="8">
         <v>0.1177984026571082</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="8">
         <v>-0.41099134505340462</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="8">
         <v>0.1177984026571082</v>
       </c>
     </row>
@@ -1208,28 +1210,28 @@
       <c r="A18" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="8">
         <v>1.00083002282587</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="8">
         <v>3.5805356646754639E-2</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="8">
         <v>27.951963520424371</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="8">
         <v>1.4025626238469663E-37</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="8">
         <v>0.92930060006922699</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="8">
         <v>1.0723594455825129</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="8">
         <v>0.92930060006922699</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="8">
         <v>1.0723594455825129</v>
       </c>
     </row>
@@ -1237,28 +1239,28 @@
       <c r="A19" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="8">
         <v>-0.10127741811073838</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="8">
         <v>9.3136739937769913E-2</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="8">
         <v>-1.0874056594466128</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="8">
         <v>0.28093591073155733</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="8">
         <v>-0.28733944539089656</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="8">
         <v>8.4784609169419808E-2</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="8">
         <v>-0.28733944539089656</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="8">
         <v>8.4784609169419808E-2</v>
       </c>
     </row>
@@ -1266,28 +1268,28 @@
       <c r="A20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="8">
         <v>0.48968427070368181</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="8">
         <v>0.10266641328866985</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="8">
         <v>4.7696637587486732</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="8">
         <v>1.1068263171043666E-5</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="8">
         <v>0.28458453237446973</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="8">
         <v>0.69478400903289383</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="8">
         <v>0.28458453237446973</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="8">
         <v>0.69478400903289383</v>
       </c>
     </row>
@@ -1295,28 +1297,28 @@
       <c r="A21" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="8">
         <v>-0.17983400015595161</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="8">
         <v>0.1472955434035966</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="8">
         <v>-1.2209059147376791</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="8">
         <v>0.22660058149958515</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="8">
         <v>-0.47409067516215575</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="8">
         <v>0.11442267485025256</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="8">
         <v>-0.47409067516215575</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="8">
         <v>0.11442267485025256</v>
       </c>
     </row>
@@ -1324,28 +1326,28 @@
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="9">
         <v>-0.2245431114933594</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="9">
         <v>0.171214394658668</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="9">
         <v>-1.3114733252481907</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="9">
         <v>0.19438341251096936</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="9">
         <v>-0.5665831849490337</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="9">
         <v>0.11749696196231493</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="9">
         <v>-0.5665831849490337</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="9">
         <v>0.11749696196231493</v>
       </c>
     </row>
